--- a/resumen_intervalos.xlsx
+++ b/resumen_intervalos.xlsx
@@ -1,52 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProyectosTEL\Respaldo_Conteo_Personas_PDI\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99C77AE5-010B-4817-96C4-EAA56B05F968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
-  <si>
-    <t>INTERVALO</t>
-  </si>
-  <si>
-    <t>MOV 1</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -65,22 +50,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -368,42 +412,47 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="22.6640625" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>INTERVALO</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>MOV 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46175.27019675926</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46175.27025462963</v>
+      </c>
+      <c r="B3" t="n">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>46175.270196759258</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>46175.270254629628</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>46175.270312499997</v>
-      </c>
-      <c r="B4">
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46175.2703125</v>
+      </c>
+      <c r="B4" t="n">
         <v>1</v>
       </c>
     </row>

--- a/resumen_intervalos.xlsx
+++ b/resumen_intervalos.xlsx
@@ -1,37 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProyectosTEL\Respaldo_Conteo_Personas_PDI\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7BB9C35-F025-46E0-BA63-633625F51714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+  <si>
+    <t>INTERVALO</t>
+  </si>
+  <si>
+    <t>MOV 1</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -50,81 +65,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -412,47 +368,42 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="27.5546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>INTERVALO</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>MOV 1</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>46175.27019675926</v>
-      </c>
-      <c r="B2" t="n">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>46175.270196759258</v>
+      </c>
+      <c r="B2">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>46175.27025462963</v>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>46175.270254629628</v>
+      </c>
+      <c r="B3">
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>46175.2703125</v>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>46175.270312499997</v>
+      </c>
+      <c r="B4">
         <v>1</v>
       </c>
     </row>

--- a/resumen_intervalos.xlsx
+++ b/resumen_intervalos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProyectosTEL\Respaldo_Conteo_Personas_PDI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7BB9C35-F025-46E0-BA63-633625F51714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D4095A-C053-44EB-A10E-86C19167D709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>INTERVALO</t>
   </si>
   <si>
     <t>MOV 1</t>
+  </si>
+  <si>
+    <t>MOV 2</t>
   </si>
 </sst>
 </file>
@@ -369,42 +372,142 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.5546875" customWidth="1"/>
+    <col min="1" max="1" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>46175.270196759258</v>
+        <v>46225.356249999997</v>
       </c>
       <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>46225.356944444437</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>46225.357638888891</v>
+      </c>
+      <c r="B4">
+        <v>19</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>46225.35833333333</v>
+      </c>
+      <c r="B5">
+        <v>12</v>
+      </c>
+      <c r="C5">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>46175.270254629628</v>
-      </c>
-      <c r="B3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>46225.359027777777</v>
+      </c>
+      <c r="B6">
+        <v>18</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>46225.359722222223</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>46225.36041666667</v>
+      </c>
+      <c r="B8">
+        <v>23</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>46225.361111111109</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>46225.361805555563</v>
+      </c>
+      <c r="B10">
+        <v>17</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>46225.362500000003</v>
+      </c>
+      <c r="B11">
+        <v>14</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>46225.363194444442</v>
+      </c>
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12">
         <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>46175.270312499997</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
